--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2342-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2342-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDF954CA-A221-4EC9-A8B7-3383ED272317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8133CAEB-EC16-4EE3-B3F6-DFA996EF00D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{F44D63F9-7286-4852-8791-CA356F79335B}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{31F43ED1-D3F7-4AAC-921D-D9B1A8E07026}"/>
   </bookViews>
   <sheets>
     <sheet name="2342-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1472,24 +1472,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A33C24D-1F36-4A1C-8935-699B09521339}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98C9DF97-A452-461A-BF99-FEC4EFF78B95}">
   <dimension ref="A1:R53"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1517,7 +1517,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1547,7 +1547,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1643,7 +1643,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1697,7 +1697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1753,7 +1753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2025</v>
       </c>
@@ -1863,7 +1863,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1919,7 +1919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2031,7 +2031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="37">
         <v>2024</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>25</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>25</v>
       </c>
@@ -2253,7 +2253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="39">
         <v>2023</v>
       </c>
@@ -2307,7 +2307,7 @@
         <v>4.91</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>25</v>
       </c>
@@ -2363,7 +2363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>25</v>
       </c>
@@ -2419,7 +2419,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
         <v>25</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="37">
         <v>2022</v>
       </c>
@@ -2529,7 +2529,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>25</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="39">
         <v>2021</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2695,7 +2695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>25</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2020</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="39">
         <v>2019</v>
       </c>
@@ -2859,7 +2859,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="37">
         <v>2018</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="39">
         <v>2017</v>
       </c>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="37">
         <v>2016</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2015</v>
       </c>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="37">
         <v>2014</v>
       </c>
@@ -3129,7 +3129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="39">
         <v>2013</v>
       </c>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="37">
         <v>2012</v>
       </c>
@@ -3237,7 +3237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="39">
         <v>2011</v>
       </c>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>2010</v>
       </c>
@@ -3345,7 +3345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="39">
         <v>2009</v>
       </c>
@@ -3399,7 +3399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
         <v>2008</v>
       </c>
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="39">
         <v>2007</v>
       </c>
@@ -3507,7 +3507,7 @@
         <v>2.69</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="37">
         <v>2006</v>
       </c>
@@ -3561,7 +3561,7 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="39">
         <v>2005</v>
       </c>
@@ -3615,7 +3615,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="37">
         <v>2004</v>
       </c>
@@ -3669,7 +3669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="39">
         <v>2003</v>
       </c>
@@ -3723,7 +3723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="37">
         <v>2002</v>
       </c>
@@ -3777,7 +3777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="39">
         <v>2001</v>
       </c>
@@ -3831,7 +3831,7 @@
         <v>5.59</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="37">
         <v>2000</v>
       </c>
@@ -3885,7 +3885,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="39">
         <v>1999</v>
       </c>
@@ -3939,7 +3939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="37">
         <v>1998</v>
       </c>
@@ -3993,7 +3993,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="39">
         <v>1997</v>
       </c>
@@ -4047,7 +4047,7 @@
         <v>4.57</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="37">
         <v>1996</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="39">
         <v>1995</v>
       </c>
@@ -4155,7 +4155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="37">
         <v>1994</v>
       </c>
@@ -4209,7 +4209,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="39">
         <v>1993</v>
       </c>
@@ -4263,7 +4263,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="37" t="s">
         <v>43</v>
       </c>
